--- a/Design/Excel/ET/Datas/Product/StationUpgradeConfig.xlsx
+++ b/Design/Excel/ET/Datas/Product/StationUpgradeConfig.xlsx
@@ -1128,7 +1128,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr/>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="6"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>GridStationKind</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>GridStationCapability</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>StationWorkKind</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -1301,17 +1301,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Chopping</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Chop</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Chop</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1348,33 +1348,306 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>Oven</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Bake</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Bake</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B6">
+        <v>3</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>高效灶台</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Stove</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Cook</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Batch</t>
+        </is>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+      <c r="H6">
+        <v>3</v>
+      </c>
+      <c r="I6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B7">
+        <v>4</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>高效榨汁机</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Juicer</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Juice</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Batch</t>
+        </is>
+      </c>
+      <c r="G7">
+        <v>1</v>
+      </c>
+      <c r="H7">
+        <v>3</v>
+      </c>
+      <c r="I7">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B8">
+        <v>5</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>高效煎台</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Frying</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Fry</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Bake</t>
+        </is>
+      </c>
+      <c r="G8">
+        <v>1</v>
+      </c>
+      <c r="H8">
+        <v>3</v>
+      </c>
+      <c r="I8">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B9">
+        <v>6</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>高效搅拌机</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Mixer</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Mixing</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Batch</t>
+        </is>
+      </c>
+      <c r="G9">
+        <v>1</v>
+      </c>
+      <c r="H9">
+        <v>3</v>
+      </c>
+      <c r="I9">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B10">
+        <v>7</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>高效磨豆机</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Grinder</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Grind</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Bake</t>
+        </is>
+      </c>
+      <c r="G10">
+        <v>1</v>
+      </c>
+      <c r="H10">
+        <v>3</v>
+      </c>
+      <c r="I10">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B11">
+        <v>8</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>高效咖啡机</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>CoffeeMachine</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Extract</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Batch</t>
+        </is>
+      </c>
+      <c r="G11">
+        <v>1</v>
+      </c>
+      <c r="H11">
+        <v>3</v>
+      </c>
+      <c r="I11">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B12">
+        <v>9</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>高效蒸汽机</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>SteamMachine</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>HeatMilk|FoamMilk</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Batch</t>
+        </is>
+      </c>
+      <c r="G12">
+        <v>1</v>
+      </c>
+      <c r="H12">
+        <v>3</v>
+      </c>
+      <c r="I12">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
